--- a/docs/Test_Report/Cdd_Adc/TestPlanExecutionReport_Cdd_Adc.xlsx
+++ b/docs/Test_Report/Cdd_Adc/TestPlanExecutionReport_Cdd_Adc.xlsx
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10 04:18:14.103709-05:00 CDT</t>
+          <t>2025-06-09 07:29:23.464156-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1727,12 +1727,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -1909,12 +1909,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2000,12 +2000,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2091,12 +2091,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2182,12 +2182,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2364,12 +2364,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2455,12 +2455,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2546,12 +2546,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -2637,12 +2637,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -2728,12 +2728,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2910,12 +2910,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3092,12 +3092,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3183,12 +3183,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -3274,12 +3274,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3365,12 +3365,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -3456,12 +3456,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -3547,12 +3547,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -3729,12 +3729,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -3820,12 +3820,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -3911,12 +3911,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -4002,12 +4002,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -4093,12 +4093,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -4184,12 +4184,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -4275,12 +4275,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -4366,12 +4366,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -4457,12 +4457,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -4548,12 +4548,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -4639,12 +4639,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -4730,12 +4730,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -4821,12 +4821,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -4912,12 +4912,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -5003,12 +5003,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -5094,12 +5094,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -5185,12 +5185,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -5276,12 +5276,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -5367,12 +5367,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -5458,12 +5458,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -5549,12 +5549,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -5731,12 +5731,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -5822,12 +5822,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -5913,12 +5913,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -6004,12 +6004,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -6186,12 +6186,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -6277,12 +6277,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -6368,12 +6368,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -6459,12 +6459,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -6550,12 +6550,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -6641,12 +6641,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -6732,12 +6732,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -6914,12 +6914,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -7005,12 +7005,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -7096,12 +7096,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -7187,12 +7187,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -7278,12 +7278,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -7369,12 +7369,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -7460,12 +7460,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -7532,12 +7532,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -7551,12 +7551,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -7642,12 +7642,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -7733,12 +7733,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -7824,12 +7824,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -7915,12 +7915,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -8006,12 +8006,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -8097,12 +8097,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -8188,12 +8188,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -8279,12 +8279,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -8370,12 +8370,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -8461,12 +8461,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -8552,12 +8552,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -8643,12 +8643,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -8734,12 +8734,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -8825,12 +8825,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -8916,12 +8916,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -9007,12 +9007,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -9098,12 +9098,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -9189,12 +9189,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
@@ -9280,12 +9280,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -9371,12 +9371,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -9462,12 +9462,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -9553,12 +9553,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -9644,12 +9644,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
@@ -9735,12 +9735,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
@@ -9826,12 +9826,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
@@ -9917,12 +9917,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
@@ -10008,12 +10008,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
@@ -10099,12 +10099,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
@@ -10190,12 +10190,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
@@ -10281,12 +10281,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
@@ -10372,12 +10372,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
@@ -10463,12 +10463,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
@@ -10554,12 +10554,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -10626,12 +10626,12 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
@@ -10645,12 +10645,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
@@ -10736,12 +10736,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
@@ -10827,12 +10827,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr"/>
@@ -10918,12 +10918,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
@@ -11009,12 +11009,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
@@ -11100,12 +11100,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
@@ -11191,12 +11191,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
@@ -11282,12 +11282,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
@@ -11373,12 +11373,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
@@ -11464,12 +11464,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
@@ -11555,12 +11555,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
@@ -11646,12 +11646,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
@@ -11737,12 +11737,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -11809,12 +11809,12 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
@@ -11828,12 +11828,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S115" s="3" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S116" s="3" t="inlineStr"/>
@@ -12010,12 +12010,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S117" s="3" t="inlineStr"/>
@@ -12101,12 +12101,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S118" s="3" t="inlineStr"/>
@@ -12192,12 +12192,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S119" s="3" t="inlineStr"/>
@@ -12283,12 +12283,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr"/>
@@ -12374,12 +12374,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr"/>
@@ -12465,12 +12465,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr"/>
@@ -12556,12 +12556,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -12628,12 +12628,12 @@
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S123" s="3" t="inlineStr"/>
@@ -12647,12 +12647,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S124" s="3" t="inlineStr"/>
@@ -12738,12 +12738,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr"/>
@@ -12829,12 +12829,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S126" s="3" t="inlineStr"/>
@@ -12920,12 +12920,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S127" s="3" t="inlineStr"/>
@@ -13011,12 +13011,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S128" s="3" t="inlineStr"/>
@@ -13102,12 +13102,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S129" s="3" t="inlineStr"/>
@@ -13193,12 +13193,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -13265,12 +13265,12 @@
       </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S130" s="3" t="inlineStr"/>
@@ -13284,12 +13284,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S131" s="3" t="inlineStr"/>
@@ -13375,12 +13375,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S132" s="3" t="inlineStr"/>
@@ -13466,12 +13466,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S133" s="3" t="inlineStr"/>
@@ -13557,12 +13557,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S134" s="3" t="inlineStr"/>
@@ -13648,12 +13648,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S135" s="3" t="inlineStr"/>
@@ -13739,12 +13739,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr"/>
@@ -13830,12 +13830,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S137" s="3" t="inlineStr"/>
@@ -13921,12 +13921,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr"/>
@@ -14012,12 +14012,12 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr"/>
@@ -14103,12 +14103,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -14175,12 +14175,12 @@
       </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr"/>
@@ -14194,12 +14194,12 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S141" s="3" t="inlineStr"/>
@@ -14285,12 +14285,12 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S142" s="3" t="inlineStr"/>
@@ -14376,12 +14376,12 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -14448,12 +14448,12 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S143" s="3" t="inlineStr"/>
@@ -14467,12 +14467,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr"/>
@@ -14558,12 +14558,12 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S145" s="3" t="inlineStr"/>
@@ -14649,12 +14649,12 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -14721,12 +14721,12 @@
       </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S146" s="3" t="inlineStr"/>
@@ -14740,12 +14740,12 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -14812,12 +14812,12 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S147" s="3" t="inlineStr"/>
@@ -14831,12 +14831,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S148" s="3" t="inlineStr"/>
@@ -14922,12 +14922,12 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -14994,12 +14994,12 @@
       </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S149" s="3" t="inlineStr"/>
@@ -15013,12 +15013,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr"/>
@@ -15104,12 +15104,12 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S151" s="3" t="inlineStr"/>
@@ -15195,12 +15195,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S152" s="3" t="inlineStr"/>
@@ -15286,12 +15286,12 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -15358,12 +15358,12 @@
       </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S153" s="3" t="inlineStr"/>
@@ -15377,12 +15377,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -15449,12 +15449,12 @@
       </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr"/>
@@ -15468,12 +15468,12 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S155" s="3" t="inlineStr"/>
@@ -15559,12 +15559,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -15631,12 +15631,12 @@
       </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr"/>
@@ -15650,12 +15650,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S157" s="3" t="inlineStr"/>
@@ -15741,12 +15741,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -15813,12 +15813,12 @@
       </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr"/>
@@ -15832,12 +15832,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S159" s="3" t="inlineStr"/>
@@ -15923,12 +15923,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -15995,12 +15995,12 @@
       </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr"/>
@@ -16014,12 +16014,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr"/>
@@ -16105,12 +16105,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr"/>
@@ -16196,12 +16196,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -16268,12 +16268,12 @@
       </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr"/>
@@ -16287,12 +16287,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -16359,12 +16359,12 @@
       </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr"/>
@@ -16378,12 +16378,12 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -16450,12 +16450,12 @@
       </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr"/>
@@ -16469,12 +16469,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S166" s="3" t="inlineStr"/>
@@ -16560,12 +16560,12 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr"/>
@@ -16651,12 +16651,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S168" s="3" t="inlineStr"/>
@@ -16742,12 +16742,12 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -16814,12 +16814,12 @@
       </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S169" s="3" t="inlineStr"/>
@@ -16833,12 +16833,12 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S170" s="3" t="inlineStr"/>
@@ -16924,12 +16924,12 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S171" s="3" t="inlineStr"/>
@@ -17015,12 +17015,12 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -17087,12 +17087,12 @@
       </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr"/>
@@ -17106,12 +17106,12 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -17178,12 +17178,12 @@
       </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr"/>
@@ -17197,12 +17197,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr"/>
@@ -17288,12 +17288,12 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -17360,12 +17360,12 @@
       </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S175" s="3" t="inlineStr"/>
@@ -17379,12 +17379,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S176" s="3" t="inlineStr"/>
@@ -17470,12 +17470,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr"/>
@@ -17561,12 +17561,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -17633,12 +17633,12 @@
       </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S178" s="3" t="inlineStr"/>
@@ -17652,12 +17652,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr"/>
@@ -17743,12 +17743,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr"/>
@@ -17834,12 +17834,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -17906,12 +17906,12 @@
       </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S181" s="3" t="inlineStr"/>
@@ -17925,12 +17925,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -17997,12 +17997,12 @@
       </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr"/>
@@ -18016,12 +18016,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18088,12 +18088,12 @@
       </c>
       <c r="Q183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr"/>
@@ -18107,12 +18107,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18179,12 +18179,12 @@
       </c>
       <c r="Q184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S184" s="3" t="inlineStr"/>
@@ -18198,12 +18198,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="Q185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr"/>
@@ -18289,12 +18289,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18361,12 +18361,12 @@
       </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S186" s="3" t="inlineStr"/>
@@ -18380,12 +18380,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="Q187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S187" s="3" t="inlineStr"/>
@@ -18471,12 +18471,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18543,12 +18543,12 @@
       </c>
       <c r="Q188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S188" s="3" t="inlineStr"/>
@@ -18562,12 +18562,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18634,12 +18634,12 @@
       </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S189" s="3" t="inlineStr"/>
@@ -18653,12 +18653,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -18725,12 +18725,12 @@
       </c>
       <c r="Q190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S190" s="3" t="inlineStr"/>
@@ -18744,12 +18744,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -18816,12 +18816,12 @@
       </c>
       <c r="Q191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S191" s="3" t="inlineStr"/>
@@ -18835,12 +18835,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -18907,12 +18907,12 @@
       </c>
       <c r="Q192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S192" s="3" t="inlineStr"/>
@@ -18926,12 +18926,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -18998,12 +18998,12 @@
       </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S193" s="3" t="inlineStr"/>
@@ -19017,12 +19017,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="Q194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S194" s="3" t="inlineStr"/>
@@ -19108,12 +19108,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -19180,12 +19180,12 @@
       </c>
       <c r="Q195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S195" s="3" t="inlineStr"/>
@@ -19199,12 +19199,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -19271,12 +19271,12 @@
       </c>
       <c r="Q196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S196" s="3" t="inlineStr"/>
@@ -19290,12 +19290,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -19362,12 +19362,12 @@
       </c>
       <c r="Q197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr"/>
@@ -19381,12 +19381,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -19453,12 +19453,12 @@
       </c>
       <c r="Q198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S198" s="3" t="inlineStr"/>
@@ -19472,12 +19472,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -19544,12 +19544,12 @@
       </c>
       <c r="Q199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S199" s="3" t="inlineStr"/>
@@ -19563,12 +19563,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -19635,12 +19635,12 @@
       </c>
       <c r="Q200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S200" s="3" t="inlineStr"/>
@@ -19654,12 +19654,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -19726,12 +19726,12 @@
       </c>
       <c r="Q201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S201" s="3" t="inlineStr"/>
@@ -19745,12 +19745,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -19817,12 +19817,12 @@
       </c>
       <c r="Q202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S202" s="3" t="inlineStr"/>
@@ -19836,12 +19836,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -19908,12 +19908,12 @@
       </c>
       <c r="Q203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S203" s="3" t="inlineStr"/>
@@ -19927,12 +19927,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30263</t>
+          <t>MCAL-30761</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Tests</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -19999,12 +19999,12 @@
       </c>
       <c r="Q204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30262</t>
+          <t>MCAL-30755</t>
         </is>
       </c>
       <c r="R204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD ADC - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD ADC - Manual Test Run</t>
         </is>
       </c>
       <c r="S204" s="3" t="inlineStr"/>
